--- a/data/trans_dic/IP04D$colectiva-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$colectiva-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -521,8 +522,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -612,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -675,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,8</t>
+          <t>0,0; 7,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,43</t>
+          <t>0,0; 3,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,82</t>
+          <t>0,0; 3,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,16</t>
+          <t>0,0; 8,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,21</t>
+          <t>0,45; 3,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,08</t>
+          <t>0,0; 3,86</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -785,54 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,12</t>
+          <t>0,57; 4,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,78</t>
+          <t>0,0; 2,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 6,15</t>
+          <t>0,65; 6,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 6,46</t>
+          <t>1,16; 6,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,98</t>
+          <t>0,0; 3,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,7</t>
+          <t>0,0; 5,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,51</t>
+          <t>1,19; 4,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,49</t>
+          <t>0,26; 2,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,44</t>
+          <t>0,77; 4,15</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -895,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,97</t>
+          <t>0,0; 6,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 9,68</t>
+          <t>0,97; 7,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,68; 19,88</t>
+          <t>7,04; 19,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,87</t>
+          <t>0,0; 5,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 7,67</t>
+          <t>0,92; 7,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,96; 28,12</t>
+          <t>11,94; 27,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,08</t>
+          <t>0,45; 4,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 6,29</t>
+          <t>1,05; 6,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,04; 21,44</t>
+          <t>10,82; 21,55</t>
         </is>
       </c>
     </row>
@@ -1005,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,92; 15,13</t>
+          <t>3,96; 15,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,88; 9,93</t>
+          <t>1,87; 10,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,47; 21,51</t>
+          <t>7,76; 21,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 9,56</t>
+          <t>0,86; 10,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 11,88</t>
+          <t>2,8; 11,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 10,62</t>
+          <t>1,22; 11,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,04; 9,92</t>
+          <t>2,93; 9,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,93; 9,13</t>
+          <t>2,76; 9,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 13,57</t>
+          <t>4,72; 13,17</t>
         </is>
       </c>
     </row>
@@ -1115,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,68; 20,14</t>
+          <t>3,67; 19,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,47; 24,29</t>
+          <t>6,71; 24,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,6; 19,22</t>
+          <t>6,96; 18,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,37</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1225,54 +1228,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,57; 14,25</t>
+          <t>2,46; 14,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,79; 28,99</t>
+          <t>11,88; 29,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33,08; 55,25</t>
+          <t>32,68; 55,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,16; 8,89</t>
+          <t>1,16; 9,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,94; 31,02</t>
+          <t>12,85; 30,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,5; 45,96</t>
+          <t>27,1; 46,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,93; 8,79</t>
+          <t>2,41; 9,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,01; 26,95</t>
+          <t>14,27; 27,03</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32,09; 47,11</t>
+          <t>32,42; 47,2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1335,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,78</t>
+          <t>0,5; 5,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,95; 7,69</t>
+          <t>1,86; 7,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,75; 15,71</t>
+          <t>5,77; 15,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,61</t>
+          <t>0,0; 2,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 6,9</t>
+          <t>1,47; 6,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,7; 12,96</t>
+          <t>5,21; 13,21</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,51</t>
+          <t>0,25; 2,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,04; 5,88</t>
+          <t>2,25; 6,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,45; 12,53</t>
+          <t>6,64; 12,42</t>
         </is>
       </c>
     </row>
@@ -1445,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,83</t>
+          <t>0,86; 4,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,39</t>
+          <t>0,33; 3,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0; 1,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,22</t>
+          <t>0,9; 5,16</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,84</t>
+          <t>0,0; 2,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,61</t>
+          <t>0,0; 2,2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,1</t>
+          <t>1,35; 4,24</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,19</t>
+          <t>0,37; 2,29</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,32</t>
+          <t>0,0; 1,1</t>
         </is>
       </c>
     </row>
@@ -1555,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,79</t>
+          <t>2,54; 4,86</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,46; 4,7</t>
+          <t>2,48; 4,84</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,25; 9,87</t>
+          <t>6,24; 9,74</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,98</t>
+          <t>2,0; 3,99</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,58; 4,84</t>
+          <t>2,62; 4,83</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,45; 8,64</t>
+          <t>5,56; 8,68</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,46; 4,02</t>
+          <t>2,46; 3,93</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,7; 4,33</t>
+          <t>2,79; 4,45</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,22; 8,48</t>
+          <t>6,17; 8,6</t>
         </is>
       </c>
     </row>
@@ -1624,4 +1627,1611 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1136</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>584</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1094</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1719</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1653</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3976</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2518</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2434</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 6359</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>551; 4646</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5896</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1957</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3197</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3204</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1333</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5161</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1904</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>5237</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>591; 4844</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2930</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>828; 8353</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1271; 7142</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4128</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 6798</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2540; 9682</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>566; 5583</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1964; 10588</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1391</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2111</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>7091</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1985</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>12239</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2088</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>4095</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>19330</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4667</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>646; 5158</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4105; 11635</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4235</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>644; 5365</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>8019; 18567</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>624; 5823</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1440; 8329</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>13568; 27033</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>6231</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3651</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8773</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2713</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4722</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>3471</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>8944</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>8373</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>12244</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>3077; 11904</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1422; 8062</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>5368; 14897</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>708; 8324</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2270; 9400</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>955; 8720</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>4693; 14898</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>4342; 14841</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>6949; 19394</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>4349</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>6587</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>10936</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1611; 8713</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>3138; 11233</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>6307; 16815</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>3637</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>10458</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>20173</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2196</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>11901</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>20174</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>5833</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>22360</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>40348</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>1358; 7782</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>6449; 15925</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>15090; 25434</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>700; 5565</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>7419; 17508</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>15229; 26155</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2788; 10488</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>15981; 30279</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>33178; 48313</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2316</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>5470</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>12331</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>4883</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>13088</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2990</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>10353</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>25419</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>700; 7060</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2535; 10444</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>7186; 18766</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3388</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2062; 9201</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>8072; 20486</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>711; 6892</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>6217; 16918</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>18566; 34737</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>3785</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>4317</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1384</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>658</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>8102</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>3399</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>658</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>1409; 7999</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>537; 5509</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>1535; 8839</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4767</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3441</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>4533; 14217</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>1234; 7671</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3163</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>24802</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>24276</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>52125</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>20972</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>26208</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>52763</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>45774</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>50484</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>104888</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>17982; 34398</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>17392; 33867</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>41484; 64809</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>15008; 30035</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>19382; 35710</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>42303; 65963</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>35902; 57350</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>40111; 64109</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>87935; 122650</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP04D$colectiva-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$colectiva-Provincia-trans_dic.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,04</t>
+          <t>0,0; 6,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,44</t>
+          <t>0,0; 4,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,76</t>
+          <t>0,0; 5,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -703,12 +703,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,01</t>
+          <t>0,0; 6,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,83</t>
+          <t>0,46; 3,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,86</t>
+          <t>0,0; 3,63</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,65</t>
+          <t>0,57; 5,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,82</t>
+          <t>0,0; 2,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,54</t>
+          <t>0,66; 6,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 6,5</t>
+          <t>1,13; 6,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,74</t>
+          <t>0,0; 4,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,33</t>
+          <t>0,0; 5,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,53</t>
+          <t>1,19; 4,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,61</t>
+          <t>0,26; 2,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,15</t>
+          <t>0,75; 4,29</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,85</t>
+          <t>0,0; 7,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 7,72</t>
+          <t>0,99; 9,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,04; 19,97</t>
+          <t>6,34; 20,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,94</t>
+          <t>0,0; 4,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 7,67</t>
+          <t>0,93; 7,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,94; 27,64</t>
+          <t>11,36; 27,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,18</t>
+          <t>0,45; 4,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 6,09</t>
+          <t>1,42; 6,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,82; 21,55</t>
+          <t>10,67; 21,23</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,96; 15,31</t>
+          <t>3,71; 15,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,87; 10,59</t>
+          <t>1,91; 10,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,76; 21,54</t>
+          <t>6,88; 21,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 10,12</t>
+          <t>0,87; 10,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,8; 11,58</t>
+          <t>1,98; 11,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 11,16</t>
+          <t>1,01; 11,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,93; 9,31</t>
+          <t>3,0; 9,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,76; 9,43</t>
+          <t>2,84; 9,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,72; 13,17</t>
+          <t>4,73; 13,11</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,67; 19,85</t>
+          <t>3,54; 19,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,71; 24,03</t>
+          <t>7,27; 24,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,96; 18,55</t>
+          <t>6,91; 18,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,46; 14,07</t>
+          <t>2,55; 14,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,88; 29,34</t>
+          <t>11,89; 30,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32,68; 55,09</t>
+          <t>32,35; 53,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,16; 9,24</t>
+          <t>1,19; 10,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,85; 30,32</t>
+          <t>12,66; 31,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,1; 46,55</t>
+          <t>25,98; 47,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,41; 9,08</t>
+          <t>2,5; 9,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,27; 27,03</t>
+          <t>14,39; 27,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32,42; 47,2</t>
+          <t>31,9; 46,67</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 5,09</t>
+          <t>0,5; 4,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,86; 7,65</t>
+          <t>1,97; 7,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,77; 15,07</t>
+          <t>5,84; 15,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,32</t>
+          <t>0,0; 2,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 6,58</t>
+          <t>1,49; 6,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,21; 13,21</t>
+          <t>5,23; 13,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,42</t>
+          <t>0,28; 2,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,25; 6,12</t>
+          <t>2,29; 6,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,64; 12,42</t>
+          <t>6,68; 12,74</t>
         </is>
       </c>
     </row>
@@ -1448,12 +1448,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,86; 4,88</t>
+          <t>0,82; 4,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,36</t>
+          <t>0,33; 3,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1463,32 +1463,32 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,16</t>
+          <t>0,89; 5,38</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,8</t>
+          <t>0,0; 2,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,2</t>
+          <t>0,0; 2,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,24</t>
+          <t>1,3; 4,09</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,29</t>
+          <t>0,37; 2,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,1</t>
+          <t>0,0; 1,07</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,54; 4,86</t>
+          <t>2,46; 4,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,48; 4,84</t>
+          <t>2,57; 4,92</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,24; 9,74</t>
+          <t>6,17; 9,65</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,0; 3,99</t>
+          <t>1,9; 3,86</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,62; 4,83</t>
+          <t>2,5; 4,78</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,56; 8,68</t>
+          <t>5,4; 8,65</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,46; 3,93</t>
+          <t>2,37; 3,98</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,79; 4,45</t>
+          <t>2,78; 4,42</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,17; 8,6</t>
+          <t>6,31; 8,62</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3976</t>
+          <t>0; 3532</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2518</t>
+          <t>0; 2938</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2434</t>
+          <t>0; 3251</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 6359</t>
+          <t>0; 5041</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>551; 4646</t>
+          <t>561; 4638</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5896</t>
+          <t>0; 5543</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>591; 4844</t>
+          <t>592; 5261</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2930</t>
+          <t>0; 2988</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>828; 8353</t>
+          <t>840; 7973</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1271; 7142</t>
+          <t>1245; 7185</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4128</t>
+          <t>0; 4634</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6798</t>
+          <t>0; 6568</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2540; 9682</t>
+          <t>2545; 10307</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>566; 5583</t>
+          <t>564; 5705</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1964; 10588</t>
+          <t>1914; 10944</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4667</t>
+          <t>0; 4907</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646; 5158</t>
+          <t>662; 6183</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4105; 11635</t>
+          <t>3693; 11656</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4235</t>
+          <t>0; 3517</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>644; 5365</t>
+          <t>649; 5354</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8019; 18567</t>
+          <t>7632; 18356</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>624; 5823</t>
+          <t>625; 6080</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1440; 8329</t>
+          <t>1942; 8264</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13568; 27033</t>
+          <t>13388; 26635</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3077; 11904</t>
+          <t>2883; 11823</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1422; 8062</t>
+          <t>1450; 7616</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5368; 14897</t>
+          <t>4758; 15177</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>708; 8324</t>
+          <t>713; 8378</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2270; 9400</t>
+          <t>1607; 9250</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>955; 8720</t>
+          <t>792; 8865</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4693; 14898</t>
+          <t>4797; 15976</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4342; 14841</t>
+          <t>4461; 14356</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6949; 19394</t>
+          <t>6963; 19304</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1611; 8713</t>
+          <t>1552; 8467</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3138; 11233</t>
+          <t>3398; 11572</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6307; 16815</t>
+          <t>6261; 16874</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1358; 7782</t>
+          <t>1410; 7861</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6449; 15925</t>
+          <t>6452; 16395</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15090; 25434</t>
+          <t>14934; 24814</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>700; 5565</t>
+          <t>716; 6556</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7419; 17508</t>
+          <t>7312; 17971</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15229; 26155</t>
+          <t>14594; 26416</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2788; 10488</t>
+          <t>2883; 10946</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15981; 30279</t>
+          <t>16118; 30361</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>33178; 48313</t>
+          <t>32646; 47771</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>700; 7060</t>
+          <t>695; 6781</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2535; 10444</t>
+          <t>2688; 10250</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7186; 18766</t>
+          <t>7277; 18774</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 3388</t>
+          <t>0; 3417</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2062; 9201</t>
+          <t>2083; 9701</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8072; 20486</t>
+          <t>8114; 20815</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>711; 6892</t>
+          <t>810; 7500</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>6217; 16918</t>
+          <t>6331; 17452</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>18566; 34737</t>
+          <t>18673; 35611</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1409; 7999</t>
+          <t>1350; 7507</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>537; 5509</t>
+          <t>535; 5592</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3017,32 +3017,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1535; 8839</t>
+          <t>1528; 9210</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 4767</t>
+          <t>0; 4887</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 3441</t>
+          <t>0; 3258</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4533; 14217</t>
+          <t>4358; 13706</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1234; 7671</t>
+          <t>1223; 7864</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 3163</t>
+          <t>0; 3081</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>17982; 34398</t>
+          <t>17440; 32935</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>17392; 33867</t>
+          <t>18023; 34452</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>41484; 64809</t>
+          <t>41031; 64200</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>15008; 30035</t>
+          <t>14277; 29047</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>19382; 35710</t>
+          <t>18514; 35369</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>42303; 65963</t>
+          <t>41076; 65804</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>35902; 57350</t>
+          <t>34629; 58113</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>40111; 64109</t>
+          <t>40100; 63666</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>87935; 122650</t>
+          <t>89985; 122939</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP04D$colectiva-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$colectiva-Provincia-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que dispone de calefacción colectiva en su vivienda (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,47 +625,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>2,01%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,26</t>
+          <t>0,0; 3,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,01</t>
+          <t>0,0; 3,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,02</t>
+          <t>0,0; 6,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -703,12 +703,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,35</t>
+          <t>0,0; 3,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,82</t>
+          <t>0,46; 4,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,63</t>
+          <t>0,0; 2,79</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>1,88%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,55%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,06</t>
+          <t>1,14; 6,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,87</t>
+          <t>0,0; 3,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,25</t>
+          <t>0,0; 5,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 6,54</t>
+          <t>0,57; 5,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,2</t>
+          <t>0,0; 2,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,15</t>
+          <t>0,82; 7,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,82</t>
+          <t>1,18; 4,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,66</t>
+          <t>0,27; 2,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 4,29</t>
+          <t>0,86; 5,0</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,84%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>18,25%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>2,04%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>3,16%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>12,17%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,2</t>
+          <t>0,0; 4,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 9,25</t>
+          <t>0,93; 7,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,34; 20,0</t>
+          <t>10,93; 27,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,94</t>
+          <t>0,0; 6,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 7,66</t>
+          <t>0,99; 9,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,36; 27,33</t>
+          <t>6,78; 20,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,36</t>
+          <t>0,45; 4,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 6,04</t>
+          <t>1,0; 6,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,67; 21,23</t>
+          <t>11,08; 21,56</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5,82%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4,76%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>8,01%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>4,8%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>12,69%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,82%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,71; 15,2</t>
+          <t>0,85; 9,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 10,0</t>
+          <t>1,96; 11,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,88; 21,95</t>
+          <t>1,24; 11,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 10,19</t>
+          <t>3,92; 15,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 11,39</t>
+          <t>1,88; 9,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 11,35</t>
+          <t>7,64; 22,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,0; 9,99</t>
+          <t>3,04; 9,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,84; 9,13</t>
+          <t>2,93; 9,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,73; 13,11</t>
+          <t>4,96; 14,53</t>
         </is>
       </c>
     </row>
@@ -1065,22 +1065,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>14,09%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>9,91%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>14,09%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,54; 19,29</t>
+          <t>7,47; 24,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,27; 24,75</t>
+          <t>3,68; 20,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,91; 18,61</t>
+          <t>7,6; 19,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>20,61%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>35,18%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>6,58%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>19,27%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>43,7%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3,65%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>20,61%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,21%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,55; 14,22</t>
+          <t>1,16; 8,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,89; 30,21</t>
+          <t>12,94; 31,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32,35; 53,75</t>
+          <t>25,9; 45,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,19; 10,88</t>
+          <t>2,57; 14,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,66; 31,12</t>
+          <t>10,79; 28,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25,98; 47,01</t>
+          <t>33,23; 55,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,5; 9,47</t>
+          <t>1,93; 8,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,39; 27,11</t>
+          <t>14,01; 26,95</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>31,9; 46,67</t>
+          <t>31,87; 46,97</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3,49%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9,33%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1,67%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>4,0%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>9,9%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,89</t>
+          <t>0,0; 2,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,97; 7,5</t>
+          <t>1,47; 6,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,84; 15,08</t>
+          <t>5,32; 14,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,34</t>
+          <t>0,51; 4,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,49; 6,93</t>
+          <t>1,95; 7,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,23; 13,42</t>
+          <t>6,13; 16,66</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,64</t>
+          <t>0,25; 2,51</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,29; 6,31</t>
+          <t>2,04; 5,88</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,68; 12,74</t>
+          <t>6,94; 13,66</t>
         </is>
       </c>
     </row>
@@ -1395,34 +1395,34 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>2,31%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>1,23%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
           <t>2,42%</t>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,17%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,58</t>
+          <t>0,87; 5,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,41</t>
+          <t>0,0; 2,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>0,0; 2,07</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0,83; 4,83</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,33; 3,39</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>0,89; 5,38</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,87</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,09</t>
-        </is>
-      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,09</t>
+          <t>1,32; 4,1</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,35</t>
+          <t>0,37; 2,19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,07</t>
+          <t>0,0; 1,01</t>
         </is>
       </c>
     </row>
@@ -1505,32 +1505,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3,54%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>6,8%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>3,5%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>3,47%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>7,84%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,46; 4,65</t>
+          <t>1,89; 3,98</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,92</t>
+          <t>2,58; 4,84</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,17; 9,65</t>
+          <t>5,36; 8,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,9; 3,86</t>
+          <t>2,57; 4,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,5; 4,78</t>
+          <t>2,46; 4,7</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,4; 8,65</t>
+          <t>6,82; 10,6</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,37; 3,98</t>
+          <t>2,46; 4,02</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,78; 4,42</t>
+          <t>2,7; 4,33</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,31; 8,62</t>
+          <t>6,42; 8,68</t>
         </is>
       </c>
     </row>
@@ -1654,20 +1654,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que dispone de calefacción colectiva en su vivienda (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1755,22 +1755,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1808,47 +1808,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>584</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>1136</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>559</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>584</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1719</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1094</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1719</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>955</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3532</t>
+          <t>0; 2476</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2938</t>
+          <t>0; 2547</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3251</t>
+          <t>0; 3841</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5041</t>
+          <t>0; 1980</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>561; 4638</t>
+          <t>561; 5110</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5543</t>
+          <t>0; 3363</t>
         </is>
       </c>
     </row>
@@ -1918,32 +1918,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1971,32 +1971,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3204</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1333</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1960</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1957</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>571</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3197</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3204</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1333</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>3363</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5237</t>
+          <t>5323</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>592; 5261</t>
+          <t>1250; 7099</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2988</t>
+          <t>0; 4390</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>840; 7973</t>
+          <t>0; 5855</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1245; 7185</t>
+          <t>592; 5326</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4634</t>
+          <t>0; 2886</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6568</t>
+          <t>831; 7569</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2545; 10307</t>
+          <t>2525; 9643</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>564; 5705</t>
+          <t>572; 5327</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1914; 10944</t>
+          <t>1873; 10857</t>
         </is>
       </c>
     </row>
@@ -2081,32 +2081,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -2134,32 +2134,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>697</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1985</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10837</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>1391</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>2111</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>7091</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>697</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1985</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12239</t>
+          <t>7089</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19330</t>
+          <t>17926</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4907</t>
+          <t>0; 3470</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>662; 6183</t>
+          <t>648; 5361</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3693; 11656</t>
+          <t>6489; 16448</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3517</t>
+          <t>0; 4750</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>649; 5354</t>
+          <t>664; 6466</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7632; 18356</t>
+          <t>3836; 11519</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>625; 6080</t>
+          <t>626; 5684</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1942; 8264</t>
+          <t>1369; 8600</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13388; 26635</t>
+          <t>12840; 24991</t>
         </is>
       </c>
     </row>
@@ -2244,32 +2244,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2297,32 +2297,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2713</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4722</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3434</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>6231</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>3651</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>8773</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2713</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4722</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3471</t>
+          <t>9061</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>12244</t>
+          <t>12495</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2883; 11823</t>
+          <t>702; 7861</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1450; 7616</t>
+          <t>1588; 9642</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4758; 15177</t>
+          <t>895; 8533</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>713; 8378</t>
+          <t>3052; 11769</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1607; 9250</t>
+          <t>1428; 7562</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>792; 8865</t>
+          <t>5327; 15383</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4797; 15976</t>
+          <t>4872; 15876</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4461; 14356</t>
+          <t>4604; 14357</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6963; 19304</t>
+          <t>7046; 20618</t>
         </is>
       </c>
     </row>
@@ -2407,22 +2407,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2460,22 +2460,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>6587</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>4349</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>6587</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1552; 8467</t>
+          <t>3494; 11355</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3398; 11572</t>
+          <t>1614; 8843</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6261; 16874</t>
+          <t>6889; 17422</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2570,32 +2570,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>36</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2196</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>11901</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>17218</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>3637</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>10458</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>20173</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2196</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>11901</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20174</t>
+          <t>19918</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>40348</t>
+          <t>37136</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1410; 7861</t>
+          <t>696; 5355</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6452; 16395</t>
+          <t>7473; 17912</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14934; 24814</t>
+          <t>12677; 22292</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>716; 6556</t>
+          <t>1421; 7877</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7312; 17971</t>
+          <t>5856; 15734</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14594; 26416</t>
+          <t>15208; 25509</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2883; 10946</t>
+          <t>2226; 10150</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16118; 30361</t>
+          <t>15688; 30192</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>32646; 47771</t>
+          <t>30183; 44481</t>
         </is>
       </c>
     </row>
@@ -2733,32 +2733,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2786,32 +2786,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>4883</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>13099</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>2316</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>5470</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>12331</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>674</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>4883</t>
-        </is>
-      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13088</t>
+          <t>13020</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>25419</t>
+          <t>26119</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>695; 6781</t>
+          <t>0; 3810</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2688; 10250</t>
+          <t>2055; 9657</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7277; 18774</t>
+          <t>7475; 19973</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 3417</t>
+          <t>705; 6637</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2083; 9701</t>
+          <t>2660; 10506</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8114; 20815</t>
+          <t>7516; 20419</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>810; 7500</t>
+          <t>717; 7134</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>6331; 17452</t>
+          <t>5637; 16260</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>18673; 35611</t>
+          <t>18237; 35908</t>
         </is>
       </c>
     </row>
@@ -2901,27 +2901,27 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2949,34 +2949,34 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>4317</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1384</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>3785</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>4317</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>1384</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>658</t>
-        </is>
-      </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
           <t>8102</t>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>522</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1350; 7507</t>
+          <t>1482; 8941</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>535; 5592</t>
+          <t>0; 4832</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
+          <t>0; 3283</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>1364; 7924</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>539; 5563</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>1528; 9210</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>0; 4887</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>0; 3258</t>
-        </is>
-      </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4358; 13706</t>
+          <t>4424; 13732</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1223; 7864</t>
+          <t>1222; 7315</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 3081</t>
+          <t>0; 3011</t>
         </is>
       </c>
     </row>
@@ -3059,32 +3059,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>82</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3112,32 +3112,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>20972</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>26208</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>47551</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>24802</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>24276</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>52125</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>20972</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>26208</t>
-        </is>
-      </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>52763</t>
+          <t>52924</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>104888</t>
+          <t>100475</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>17440; 32935</t>
+          <t>14210; 29957</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>18023; 34452</t>
+          <t>19093; 35833</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>41031; 64200</t>
+          <t>37489; 59236</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14277; 29047</t>
+          <t>18213; 33912</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>18514; 35369</t>
+          <t>17194; 32882</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>41076; 65804</t>
+          <t>42864; 66630</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34629; 58113</t>
+          <t>35876; 58667</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>40100; 63666</t>
+          <t>38814; 62323</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>89985; 122939</t>
+          <t>85194; 115246</t>
         </is>
       </c>
     </row>
